--- a/output/pdf_financials_xlsx/AMQ.xlsx
+++ b/output/pdf_financials_xlsx/AMQ.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.391239</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.462067</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.108534</v>
       </c>
     </row>
     <row r="93">
@@ -3137,7 +3137,11 @@
           <t>Reserve (notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3387,7 +3391,11 @@
           <t>Reserve (note 7)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.391239</v>
       </c>

--- a/output/pdf_financials_xlsx/AMQ.xlsx
+++ b/output/pdf_financials_xlsx/AMQ.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.031512</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.367641</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.544716</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.47044</v>
+        <v>-0.501952</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.412599</v>
+        <v>-2.78024</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.523089</v>
+        <v>-3.067805</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.47044</v>
+        <v>-0.501952</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.412599</v>
+        <v>-2.78024</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.523089</v>
+        <v>-3.067805</v>
       </c>
     </row>
     <row r="30">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.012964</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>15.665569</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>16.265876</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.012964</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.035</v>
+        <v>15.700569</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.1425</v>
+        <v>16.408376</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.020812</v>
+        <v>0.007848000000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>16.180198</v>
+        <v>0.514629</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>16.323743</v>
+        <v>0.057867</v>
       </c>
     </row>
     <row r="49">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">

--- a/output/pdf_financials_xlsx/AMQ.xlsx
+++ b/output/pdf_financials_xlsx/AMQ.xlsx
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.03999</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.118905</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.03594</v>
       </c>
     </row>
     <row r="68">
@@ -3575,7 +3575,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.288</v>
       </c>
